--- a/database/event/8263/event_8263_evp_summary.xlsx
+++ b/database/event/8263/event_8263_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EVP_Summary_8263" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8263" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>2.0663</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5967</v>
+        <v>2.9428</v>
       </c>
       <c r="E2" t="n">
         <v>8.327500000000001</v>
@@ -548,7 +548,7 @@
         <v>1.8351</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2518</v>
+        <v>2.5663</v>
       </c>
       <c r="E3" t="n">
         <v>7.3955</v>
@@ -594,7 +594,7 @@
         <v>1.502</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7552</v>
+        <v>2.024</v>
       </c>
       <c r="E4" t="n">
         <v>6.0532</v>
@@ -640,7 +640,7 @@
         <v>1.4757</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7159</v>
+        <v>1.9811</v>
       </c>
       <c r="E5" t="n">
         <v>5.9471</v>
@@ -686,7 +686,7 @@
         <v>1.4183</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6303</v>
+        <v>1.8877</v>
       </c>
       <c r="E6" t="n">
         <v>5.7158</v>
@@ -732,7 +732,7 @@
         <v>1.3514</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5306</v>
+        <v>1.7788</v>
       </c>
       <c r="E7" t="n">
         <v>5.4463</v>
@@ -778,7 +778,7 @@
         <v>1.2366</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3594</v>
+        <v>1.5919</v>
       </c>
       <c r="E8" t="n">
         <v>4.9836</v>
@@ -824,7 +824,7 @@
         <v>1.1624</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2489</v>
+        <v>1.4712</v>
       </c>
       <c r="E9" t="n">
         <v>4.6848</v>
@@ -870,7 +870,7 @@
         <v>0.9771</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9724</v>
+        <v>1.1694</v>
       </c>
       <c r="E10" t="n">
         <v>3.9377</v>
@@ -916,7 +916,7 @@
         <v>0.9442</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9234</v>
+        <v>1.1159</v>
       </c>
       <c r="E11" t="n">
         <v>3.8053</v>
@@ -962,7 +962,7 @@
         <v>0.9317</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9048</v>
+        <v>1.0955</v>
       </c>
       <c r="E12" t="n">
         <v>3.7549</v>
@@ -1008,7 +1008,7 @@
         <v>0.9211</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8889</v>
+        <v>1.0782</v>
       </c>
       <c r="E13" t="n">
         <v>3.712</v>
@@ -1054,7 +1054,7 @@
         <v>0.8981</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8547</v>
+        <v>1.0409</v>
       </c>
       <c r="E14" t="n">
         <v>3.6196</v>
@@ -1100,7 +1100,7 @@
         <v>0.7988</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7066</v>
+        <v>0.8791</v>
       </c>
       <c r="E15" t="n">
         <v>3.2192</v>
@@ -1146,7 +1146,7 @@
         <v>0.7827</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6826</v>
+        <v>0.8529</v>
       </c>
       <c r="E16" t="n">
         <v>3.1543</v>
@@ -1192,7 +1192,7 @@
         <v>0.7826</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6825</v>
+        <v>0.8528</v>
       </c>
       <c r="E17" t="n">
         <v>3.1541</v>
@@ -1238,7 +1238,7 @@
         <v>0.7776</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6751</v>
+        <v>0.8447</v>
       </c>
       <c r="E18" t="n">
         <v>3.134</v>
@@ -1284,7 +1284,7 @@
         <v>0.6909</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5457</v>
+        <v>0.7034</v>
       </c>
       <c r="E19" t="n">
         <v>2.7843</v>
@@ -1330,7 +1330,7 @@
         <v>0.5515</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3379</v>
+        <v>0.4766</v>
       </c>
       <c r="E20" t="n">
         <v>2.2227</v>
@@ -1376,7 +1376,7 @@
         <v>0.5354</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3138</v>
+        <v>0.4503</v>
       </c>
       <c r="E21" t="n">
         <v>2.1577</v>
@@ -1422,7 +1422,7 @@
         <v>0.5279</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3026</v>
+        <v>0.4381</v>
       </c>
       <c r="E22" t="n">
         <v>2.1274</v>
@@ -1468,7 +1468,7 @@
         <v>0.5024</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2646</v>
+        <v>0.3966</v>
       </c>
       <c r="E23" t="n">
         <v>2.0247</v>
@@ -1514,7 +1514,7 @@
         <v>0.4561</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1957</v>
+        <v>0.3213</v>
       </c>
       <c r="E24" t="n">
         <v>1.8383</v>
@@ -1560,7 +1560,7 @@
         <v>0.4538</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1922</v>
+        <v>0.3175</v>
       </c>
       <c r="E25" t="n">
         <v>1.8289</v>
@@ -1606,7 +1606,7 @@
         <v>0.4346</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1636</v>
+        <v>0.2862</v>
       </c>
       <c r="E26" t="n">
         <v>1.7516</v>
@@ -1652,7 +1652,7 @@
         <v>0.4184</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1395</v>
+        <v>0.2599</v>
       </c>
       <c r="E27" t="n">
         <v>1.6864</v>
@@ -1698,7 +1698,7 @@
         <v>0.4161</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1359</v>
+        <v>0.2561</v>
       </c>
       <c r="E28" t="n">
         <v>1.6769</v>
@@ -1744,7 +1744,7 @@
         <v>0.381</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0837</v>
+        <v>0.199</v>
       </c>
       <c r="E29" t="n">
         <v>1.5356</v>
@@ -1790,7 +1790,7 @@
         <v>0.3494</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0365</v>
+        <v>0.1475</v>
       </c>
       <c r="E30" t="n">
         <v>1.4081</v>
@@ -1836,7 +1836,7 @@
         <v>0.3377</v>
       </c>
       <c r="D31" t="n">
-        <v>0.019</v>
+        <v>0.1284</v>
       </c>
       <c r="E31" t="n">
         <v>1.3608</v>
@@ -1882,7 +1882,7 @@
         <v>0.3267</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0026</v>
+        <v>0.1105</v>
       </c>
       <c r="E32" t="n">
         <v>1.3165</v>
@@ -1928,7 +1928,7 @@
         <v>0.2944</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0456</v>
+        <v>0.0579</v>
       </c>
       <c r="E33" t="n">
         <v>1.1863</v>
@@ -1974,7 +1974,7 @@
         <v>0.2361</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1325</v>
+        <v>-0.037</v>
       </c>
       <c r="E34" t="n">
         <v>0.9515</v>
@@ -2020,7 +2020,7 @@
         <v>0.2266</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1466</v>
+        <v>-0.0524</v>
       </c>
       <c r="E35" t="n">
         <v>0.9132</v>
@@ -2066,7 +2066,7 @@
         <v>0.2207</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1554</v>
+        <v>-0.062</v>
       </c>
       <c r="E36" t="n">
         <v>0.8895</v>
@@ -2112,7 +2112,7 @@
         <v>0.2196</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1571</v>
+        <v>-0.0639</v>
       </c>
       <c r="E37" t="n">
         <v>0.8849</v>
@@ -2158,7 +2158,7 @@
         <v>0.2091</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1726</v>
+        <v>-0.0808</v>
       </c>
       <c r="E38" t="n">
         <v>0.8429</v>
@@ -2204,7 +2204,7 @@
         <v>0.2076</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1749</v>
+        <v>-0.0833</v>
       </c>
       <c r="E39" t="n">
         <v>0.8368</v>
@@ -2250,7 +2250,7 @@
         <v>0.1815</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2139</v>
+        <v>-0.1259</v>
       </c>
       <c r="E40" t="n">
         <v>0.7313</v>
@@ -2296,7 +2296,7 @@
         <v>0.154</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2548</v>
+        <v>-0.1706</v>
       </c>
       <c r="E41" t="n">
         <v>0.6208</v>
@@ -2342,7 +2342,7 @@
         <v>0.1518</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2582</v>
+        <v>-0.1743</v>
       </c>
       <c r="E42" t="n">
         <v>0.6116</v>
@@ -2388,7 +2388,7 @@
         <v>0.1315</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2884</v>
+        <v>-0.2072</v>
       </c>
       <c r="E43" t="n">
         <v>0.5301</v>
@@ -2434,7 +2434,7 @@
         <v>0.1089</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3221</v>
+        <v>-0.244</v>
       </c>
       <c r="E44" t="n">
         <v>0.439</v>
@@ -2480,7 +2480,7 @@
         <v>0.0785</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3674</v>
+        <v>-0.2935</v>
       </c>
       <c r="E45" t="n">
         <v>0.3164</v>
@@ -2526,7 +2526,7 @@
         <v>0.0727</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3761</v>
+        <v>-0.303</v>
       </c>
       <c r="E46" t="n">
         <v>0.293</v>
@@ -2572,7 +2572,7 @@
         <v>0.0673</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3842</v>
+        <v>-0.3118</v>
       </c>
       <c r="E47" t="n">
         <v>0.2711</v>
@@ -2618,7 +2618,7 @@
         <v>0.0636</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3896</v>
+        <v>-0.3177</v>
       </c>
       <c r="E48" t="n">
         <v>0.2565</v>
@@ -2664,7 +2664,7 @@
         <v>0.0615</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3928</v>
+        <v>-0.3212</v>
       </c>
       <c r="E49" t="n">
         <v>0.248</v>
@@ -2710,7 +2710,7 @@
         <v>0.0526</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4062</v>
+        <v>-0.3358</v>
       </c>
       <c r="E50" t="n">
         <v>0.2118</v>
@@ -2756,7 +2756,7 @@
         <v>0.0333</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4348</v>
+        <v>-0.3671</v>
       </c>
       <c r="E51" t="n">
         <v>0.1343</v>
@@ -2802,7 +2802,7 @@
         <v>0.0177</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4581</v>
+        <v>-0.3925</v>
       </c>
       <c r="E52" t="n">
         <v>0.07149999999999999</v>
@@ -2848,7 +2848,7 @@
         <v>0.0176</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4582</v>
+        <v>-0.3927</v>
       </c>
       <c r="E53" t="n">
         <v>0.07099999999999999</v>
@@ -2894,7 +2894,7 @@
         <v>0.0137</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.464</v>
+        <v>-0.399</v>
       </c>
       <c r="E54" t="n">
         <v>0.0554</v>
@@ -2940,7 +2940,7 @@
         <v>0.0121</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4665</v>
+        <v>-0.4017</v>
       </c>
       <c r="E55" t="n">
         <v>0.0486</v>
@@ -2986,7 +2986,7 @@
         <v>-0.0019</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4874</v>
+        <v>-0.4245</v>
       </c>
       <c r="E56" t="n">
         <v>-0.0077</v>
@@ -3032,7 +3032,7 @@
         <v>-0.0142</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5056</v>
+        <v>-0.4444</v>
       </c>
       <c r="E57" t="n">
         <v>-0.0571</v>
@@ -3078,7 +3078,7 @@
         <v>-0.0325</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.533</v>
+        <v>-0.4743</v>
       </c>
       <c r="E58" t="n">
         <v>-0.131</v>
@@ -3124,7 +3124,7 @@
         <v>-0.0543</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5655</v>
+        <v>-0.5098</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2188</v>
@@ -3170,7 +3170,7 @@
         <v>-0.061</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5754</v>
+        <v>-0.5206</v>
       </c>
       <c r="E60" t="n">
         <v>-0.2457</v>
@@ -3216,7 +3216,7 @@
         <v>-0.0906</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6196</v>
+        <v>-0.5689</v>
       </c>
       <c r="E61" t="n">
         <v>-0.3651</v>
@@ -3262,7 +3262,7 @@
         <v>-0.1022</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6369</v>
+        <v>-0.5878</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4119</v>
@@ -3308,7 +3308,7 @@
         <v>-0.1102</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6489</v>
+        <v>-0.6008</v>
       </c>
       <c r="E63" t="n">
         <v>-0.4443</v>
@@ -3354,7 +3354,7 @@
         <v>-0.1185</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6612</v>
+        <v>-0.6143</v>
       </c>
       <c r="E64" t="n">
         <v>-0.4775</v>
@@ -3400,7 +3400,7 @@
         <v>-0.1185</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6613</v>
+        <v>-0.6143</v>
       </c>
       <c r="E65" t="n">
         <v>-0.4777</v>
@@ -3446,7 +3446,7 @@
         <v>-0.1226</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6673</v>
+        <v>-0.621</v>
       </c>
       <c r="E66" t="n">
         <v>-0.4941</v>
@@ -3492,7 +3492,7 @@
         <v>-0.1262</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.6727</v>
+        <v>-0.6268</v>
       </c>
       <c r="E67" t="n">
         <v>-0.5085</v>
@@ -3538,7 +3538,7 @@
         <v>-0.1511</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7098</v>
+        <v>-0.6673</v>
       </c>
       <c r="E68" t="n">
         <v>-0.6088</v>
@@ -3584,7 +3584,7 @@
         <v>-0.1532</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7129</v>
+        <v>-0.6707</v>
       </c>
       <c r="E69" t="n">
         <v>-0.6173</v>
@@ -3630,7 +3630,7 @@
         <v>-0.1952</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7756</v>
+        <v>-0.7392</v>
       </c>
       <c r="E70" t="n">
         <v>-0.7868000000000001</v>
@@ -3676,7 +3676,7 @@
         <v>-0.226</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8216</v>
+        <v>-0.7893</v>
       </c>
       <c r="E71" t="n">
         <v>-0.9109</v>
@@ -3722,7 +3722,7 @@
         <v>-0.2481</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8545</v>
+        <v>-0.8253</v>
       </c>
       <c r="E72" t="n">
         <v>-1</v>
@@ -3768,7 +3768,7 @@
         <v>-0.2837</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9075</v>
+        <v>-0.8832</v>
       </c>
       <c r="E73" t="n">
         <v>-1.1432</v>
@@ -3814,7 +3814,7 @@
         <v>-0.2837</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9076</v>
+        <v>-0.8833</v>
       </c>
       <c r="E74" t="n">
         <v>-1.1434</v>
@@ -3860,7 +3860,7 @@
         <v>-0.2986</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9298</v>
+        <v>-0.9075</v>
       </c>
       <c r="E75" t="n">
         <v>-1.2034</v>
@@ -3906,7 +3906,7 @@
         <v>-0.3201</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9619</v>
+        <v>-0.9425</v>
       </c>
       <c r="E76" t="n">
         <v>-1.2901</v>
@@ -3952,7 +3952,7 @@
         <v>-0.3676</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0327</v>
+        <v>-1.0199</v>
       </c>
       <c r="E77" t="n">
         <v>-1.4816</v>
@@ -3998,7 +3998,7 @@
         <v>-0.381</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0527</v>
+        <v>-1.0417</v>
       </c>
       <c r="E78" t="n">
         <v>-1.5356</v>
@@ -4044,7 +4044,7 @@
         <v>-0.4059</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0897</v>
+        <v>-1.0821</v>
       </c>
       <c r="E79" t="n">
         <v>-1.6357</v>
@@ -4090,7 +4090,7 @@
         <v>-0.4499</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1553</v>
+        <v>-1.1538</v>
       </c>
       <c r="E80" t="n">
         <v>-1.813</v>
@@ -4136,7 +4136,7 @@
         <v>-0.7085</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.541</v>
+        <v>-1.5749</v>
       </c>
       <c r="E81" t="n">
         <v>-2.8554</v>
@@ -4182,7 +4182,7 @@
         <v>-1.0382</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.0326</v>
+        <v>-2.1116</v>
       </c>
       <c r="E82" t="n">
         <v>-4.1839</v>
@@ -4228,7 +4228,7 @@
         <v>-1.5369</v>
       </c>
       <c r="D83" t="n">
-        <v>-2.7762</v>
+        <v>-2.9235</v>
       </c>
       <c r="E83" t="n">
         <v>-6.1937</v>

--- a/database/event/8263/event_8263_evp_summary.xlsx
+++ b/database/event/8263/event_8263_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.327500000000001</v>
+        <v>8.453799999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0663</v>
+        <v>2.0977</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9428</v>
+        <v>2.9241</v>
       </c>
       <c r="E2" t="n">
-        <v>8.327500000000001</v>
+        <v>8.453799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6604</v>
+        <v>1.7867</v>
       </c>
       <c r="G2" t="n">
         <v>6.6671</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6604</v>
+        <v>1.7867</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6604</v>
+        <v>1.7867</v>
       </c>
       <c r="J2" t="n">
         <v>8.319800000000001</v>
@@ -529,7 +529,7 @@
         <v>200</v>
       </c>
       <c r="M2" t="n">
-        <v>9.9802</v>
+        <v>10.1065</v>
       </c>
       <c r="N2" t="n">
         <v>328</v>
@@ -548,7 +548,7 @@
         <v>1.8351</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5663</v>
+        <v>2.5025</v>
       </c>
       <c r="E3" t="n">
         <v>7.3955</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0532</v>
+        <v>6.631</v>
       </c>
       <c r="C4" t="n">
-        <v>1.502</v>
+        <v>1.6454</v>
       </c>
       <c r="D4" t="n">
-        <v>2.024</v>
+        <v>2.1979</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0532</v>
+        <v>6.631</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4293</v>
+        <v>2.0071</v>
       </c>
       <c r="G4" t="n">
         <v>4.6239</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4293</v>
+        <v>2.0071</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4293</v>
+        <v>2.0071</v>
       </c>
       <c r="J4" t="n">
         <v>4.6239</v>
@@ -621,7 +621,7 @@
         <v>200</v>
       </c>
       <c r="M4" t="n">
-        <v>6.0532</v>
+        <v>6.631</v>
       </c>
       <c r="N4" t="n">
         <v>328</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9471</v>
+        <v>5.9152</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4757</v>
+        <v>1.4677</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9811</v>
+        <v>1.9127</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9471</v>
+        <v>5.9152</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3295</v>
+        <v>4.2976</v>
       </c>
       <c r="G5" t="n">
         <v>1.6175</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4857</v>
+        <v>4.4357</v>
       </c>
       <c r="I5" t="n">
         <v>4.5486</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7158</v>
+        <v>5.8537</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4183</v>
+        <v>1.4525</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8877</v>
+        <v>1.8882</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7158</v>
+        <v>5.8537</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5398</v>
+        <v>5.4095</v>
       </c>
       <c r="G6" t="n">
-        <v>1.176</v>
+        <v>0.4442</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7042</v>
+        <v>6.1791</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6234</v>
+        <v>6.3364</v>
       </c>
       <c r="J6" t="n">
-        <v>1.176</v>
+        <v>0.4442</v>
       </c>
       <c r="K6" t="n">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="M6" t="n">
-        <v>5.7994</v>
+        <v>6.780600000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>186</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.4463</v>
+        <v>5.7158</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3514</v>
+        <v>1.4183</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7788</v>
+        <v>1.8333</v>
       </c>
       <c r="E7" t="n">
-        <v>5.4463</v>
+        <v>5.7158</v>
       </c>
       <c r="F7" t="n">
-        <v>5.0021</v>
+        <v>4.5398</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4442</v>
+        <v>1.176</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5402</v>
+        <v>5.7042</v>
       </c>
       <c r="I7" t="n">
-        <v>5.6179</v>
+        <v>4.6234</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4442</v>
+        <v>1.176</v>
       </c>
       <c r="K7" t="n">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="L7" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="M7" t="n">
-        <v>6.0621</v>
+        <v>5.7994</v>
       </c>
       <c r="N7" t="n">
-        <v>263</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8">
@@ -778,7 +778,7 @@
         <v>1.2366</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5919</v>
+        <v>1.5416</v>
       </c>
       <c r="E8" t="n">
         <v>4.9836</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6848</v>
+        <v>4.6483</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1624</v>
+        <v>1.1534</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4712</v>
+        <v>1.408</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6848</v>
+        <v>4.6483</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2739</v>
+        <v>3.2374</v>
       </c>
       <c r="G9" t="n">
         <v>1.4109</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2739</v>
+        <v>3.2374</v>
       </c>
       <c r="I9" t="n">
         <v>3.3199</v>
@@ -860,584 +860,584 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>venomzera</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9377</v>
+        <v>4.0312</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9771</v>
+        <v>1.0003</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1694</v>
+        <v>1.1621</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9377</v>
+        <v>4.0312</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2107</v>
+        <v>4.0312</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.273</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.38</v>
+        <v>4.0312</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5501</v>
+        <v>4.0312</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.273</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L10" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2771</v>
+        <v>4.0312</v>
       </c>
       <c r="N10" t="n">
-        <v>186</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>venomzera</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8053</v>
+        <v>3.9775</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9442</v>
+        <v>0.9869</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1159</v>
+        <v>1.1407</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8053</v>
+        <v>3.9775</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4774</v>
+        <v>4.2505</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3279</v>
+        <v>-0.273</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4774</v>
+        <v>4.5403</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4774</v>
+        <v>3.6801</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3279</v>
+        <v>-0.273</v>
       </c>
       <c r="K11" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="L11" t="n">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8053</v>
+        <v>3.4071</v>
       </c>
       <c r="N11" t="n">
-        <v>328</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>kl1m</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.7549</v>
+        <v>3.9555</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9317</v>
+        <v>0.9815</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0955</v>
+        <v>1.132</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7549</v>
+        <v>3.9555</v>
       </c>
       <c r="F12" t="n">
-        <v>3.874</v>
+        <v>3.9377</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1191</v>
+        <v>0.0178</v>
       </c>
       <c r="H12" t="n">
-        <v>3.874</v>
+        <v>3.9377</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9284</v>
+        <v>3.1916</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1191</v>
+        <v>0.0178</v>
       </c>
       <c r="K12" t="n">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="L12" t="n">
-        <v>126</v>
+        <v>46</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8093</v>
+        <v>3.2094</v>
       </c>
       <c r="N12" t="n">
-        <v>331</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kl1m</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.712</v>
+        <v>3.8703</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9211</v>
+        <v>0.9603</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0782</v>
+        <v>1.098</v>
       </c>
       <c r="E13" t="n">
-        <v>3.712</v>
+        <v>3.8703</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6942</v>
+        <v>1.5424</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0178</v>
+        <v>2.3279</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6942</v>
+        <v>1.5424</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9942</v>
+        <v>1.5424</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0178</v>
+        <v>2.3279</v>
       </c>
       <c r="K13" t="n">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="L13" t="n">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="M13" t="n">
-        <v>3.012</v>
+        <v>3.8703</v>
       </c>
       <c r="N13" t="n">
-        <v>186</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.6196</v>
+        <v>3.7117</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8981</v>
+        <v>0.921</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0409</v>
+        <v>1.0348</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6196</v>
+        <v>3.7117</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9607</v>
+        <v>3.8308</v>
       </c>
       <c r="G14" t="n">
-        <v>1.659</v>
+        <v>-0.1191</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9607</v>
+        <v>3.8308</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5892</v>
+        <v>3.9284</v>
       </c>
       <c r="J14" t="n">
-        <v>1.659</v>
+        <v>-0.1191</v>
       </c>
       <c r="K14" t="n">
-        <v>124</v>
+        <v>205</v>
       </c>
       <c r="L14" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2482</v>
+        <v>3.8093</v>
       </c>
       <c r="N14" t="n">
-        <v>271</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.2192</v>
+        <v>3.6614</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7988</v>
+        <v>0.9085</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8791</v>
+        <v>1.0148</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2192</v>
+        <v>3.6614</v>
       </c>
       <c r="F15" t="n">
-        <v>4.1911</v>
+        <v>3.0508</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9719</v>
+        <v>0.6106</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3012</v>
+        <v>3.0508</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4862</v>
+        <v>3.1285</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9719</v>
+        <v>0.6106</v>
       </c>
       <c r="K15" t="n">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="L15" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5143</v>
+        <v>3.7391</v>
       </c>
       <c r="N15" t="n">
-        <v>186</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.1543</v>
+        <v>3.6196</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7827</v>
+        <v>0.8981</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8529</v>
+        <v>0.9981</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1543</v>
+        <v>3.6196</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1543</v>
+        <v>1.9607</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.659</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1543</v>
+        <v>1.9607</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1543</v>
+        <v>1.5892</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.659</v>
       </c>
       <c r="K16" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1543</v>
+        <v>3.2482</v>
       </c>
       <c r="N16" t="n">
-        <v>144</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.1541</v>
+        <v>3.2209</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7826</v>
+        <v>0.7992</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8528</v>
+        <v>0.8393</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1541</v>
+        <v>3.2209</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2462</v>
+        <v>4.1928</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9079</v>
+        <v>-0.9719</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2462</v>
+        <v>4.308</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2462</v>
+        <v>3.4918</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9079</v>
+        <v>-0.9719</v>
       </c>
       <c r="K17" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="L17" t="n">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1541</v>
+        <v>2.5199</v>
       </c>
       <c r="N17" t="n">
-        <v>328</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.134</v>
+        <v>3.1541</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7776</v>
+        <v>0.7826</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8447</v>
+        <v>0.8127</v>
       </c>
       <c r="E18" t="n">
-        <v>3.134</v>
+        <v>3.1541</v>
       </c>
       <c r="F18" t="n">
-        <v>3.7391</v>
+        <v>1.2462</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6051</v>
+        <v>1.9079</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7391</v>
+        <v>1.2462</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7916</v>
+        <v>1.2462</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6051</v>
+        <v>1.9079</v>
       </c>
       <c r="K18" t="n">
-        <v>205</v>
+        <v>128</v>
       </c>
       <c r="L18" t="n">
-        <v>126</v>
+        <v>200</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1865</v>
+        <v>3.1541</v>
       </c>
       <c r="N18" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.7843</v>
+        <v>3.0924</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6909</v>
+        <v>0.7673</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7034</v>
+        <v>0.7881</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7843</v>
+        <v>3.0924</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1737</v>
+        <v>3.6975</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6106</v>
+        <v>-0.6051</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1737</v>
+        <v>3.6975</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2042</v>
+        <v>3.7916</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6106</v>
+        <v>-0.6051</v>
       </c>
       <c r="K19" t="n">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="L19" t="n">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8148</v>
+        <v>3.1865</v>
       </c>
       <c r="N19" t="n">
-        <v>263</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2227</v>
+        <v>2.6431</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5515</v>
+        <v>0.6558</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4766</v>
+        <v>0.6091</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2227</v>
+        <v>2.6431</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2227</v>
+        <v>2.6431</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2227</v>
+        <v>2.6431</v>
       </c>
       <c r="I20" t="n">
-        <v>2.233</v>
+        <v>2.6431</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.233</v>
+        <v>2.6431</v>
       </c>
       <c r="N20" t="n">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.1577</v>
+        <v>2.4356</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5354</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4503</v>
+        <v>0.5264</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1577</v>
+        <v>2.4356</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0164</v>
+        <v>2.5173</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1413</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0164</v>
+        <v>2.5173</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6344</v>
+        <v>2.5385</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1413</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="L21" t="n">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7757</v>
+        <v>2.4568</v>
       </c>
       <c r="N21" t="n">
-        <v>271</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1274</v>
+        <v>2.2144</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5279</v>
+        <v>0.5495</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4381</v>
+        <v>0.4383</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1274</v>
+        <v>2.2144</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1274</v>
+        <v>2.2144</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1274</v>
+        <v>2.2144</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1373</v>
+        <v>2.233</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.1373</v>
+        <v>2.233</v>
       </c>
       <c r="N22" t="n">
         <v>154</v>
@@ -1458,124 +1458,124 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.0247</v>
+        <v>2.1577</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5024</v>
+        <v>0.5354</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3966</v>
+        <v>0.4157</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0247</v>
+        <v>2.1577</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0247</v>
+        <v>2.0164</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.1413</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0247</v>
+        <v>2.0164</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0247</v>
+        <v>1.6344</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.1413</v>
       </c>
       <c r="K23" t="n">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M23" t="n">
-        <v>2.0247</v>
+        <v>1.7757</v>
       </c>
       <c r="N23" t="n">
-        <v>141</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8383</v>
+        <v>2.1194</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4561</v>
+        <v>0.5259</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3213</v>
+        <v>0.4005</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8383</v>
+        <v>2.1194</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8383</v>
+        <v>2.1194</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8383</v>
+        <v>2.1194</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8383</v>
+        <v>2.1373</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.8383</v>
+        <v>2.1373</v>
       </c>
       <c r="N24" t="n">
-        <v>120</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C4LLM3SU3</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8289</v>
+        <v>1.8383</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4538</v>
+        <v>0.4561</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3175</v>
+        <v>0.2885</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8289</v>
+        <v>1.8383</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8289</v>
+        <v>1.8383</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8289</v>
+        <v>1.8383</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8289</v>
+        <v>1.8383</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8289</v>
+        <v>1.8383</v>
       </c>
       <c r="N25" t="n">
         <v>120</v>
@@ -1596,323 +1596,323 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>C4LLM3SU3</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7516</v>
+        <v>1.8289</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4346</v>
+        <v>0.4538</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2862</v>
+        <v>0.2847</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7516</v>
+        <v>1.8289</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7516</v>
+        <v>1.8289</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7516</v>
+        <v>1.8289</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7516</v>
+        <v>1.8289</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7516</v>
+        <v>1.8289</v>
       </c>
       <c r="N26" t="n">
-        <v>158</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>alex666</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6864</v>
+        <v>1.7516</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4184</v>
+        <v>0.4346</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2599</v>
+        <v>0.2539</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6864</v>
+        <v>1.7516</v>
       </c>
       <c r="F27" t="n">
-        <v>2.1566</v>
+        <v>1.7516</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4702</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.1566</v>
+        <v>1.7516</v>
       </c>
       <c r="I27" t="n">
-        <v>2.1666</v>
+        <v>1.7516</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4702</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="L27" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6964</v>
+        <v>1.7516</v>
       </c>
       <c r="N27" t="n">
-        <v>207</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>alex666</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6769</v>
+        <v>1.6783</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4161</v>
+        <v>0.4164</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2561</v>
+        <v>0.2247</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6769</v>
+        <v>1.6783</v>
       </c>
       <c r="F28" t="n">
-        <v>0.785</v>
+        <v>2.1485</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8919</v>
+        <v>-0.4702</v>
       </c>
       <c r="H28" t="n">
-        <v>0.785</v>
+        <v>2.1485</v>
       </c>
       <c r="I28" t="n">
-        <v>0.796</v>
+        <v>2.1666</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8919</v>
+        <v>-0.4702</v>
       </c>
       <c r="K28" t="n">
-        <v>205</v>
+        <v>144</v>
       </c>
       <c r="L28" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6879</v>
+        <v>1.6964</v>
       </c>
       <c r="N28" t="n">
-        <v>331</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5356</v>
+        <v>1.6681</v>
       </c>
       <c r="C29" t="n">
-        <v>0.381</v>
+        <v>0.4139</v>
       </c>
       <c r="D29" t="n">
-        <v>0.199</v>
+        <v>0.2207</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5356</v>
+        <v>1.6681</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6173</v>
+        <v>0.7762</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.8919</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6173</v>
+        <v>0.7762</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6248</v>
+        <v>0.796</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.8919</v>
       </c>
       <c r="K29" t="n">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="L29" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5431</v>
+        <v>1.6879</v>
       </c>
       <c r="N29" t="n">
-        <v>207</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4081</v>
+        <v>1.5147</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3494</v>
+        <v>0.3758</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1475</v>
+        <v>0.1595</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4081</v>
+        <v>1.5147</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4081</v>
+        <v>1.5147</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4081</v>
+        <v>1.5147</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4081</v>
+        <v>1.5147</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4081</v>
+        <v>1.5147</v>
       </c>
       <c r="N30" t="n">
-        <v>136</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3608</v>
+        <v>1.4081</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3377</v>
+        <v>0.3494</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1284</v>
+        <v>0.1171</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3608</v>
+        <v>1.4081</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3608</v>
+        <v>1.4081</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.3608</v>
+        <v>1.4081</v>
       </c>
       <c r="I31" t="n">
-        <v>1.3671</v>
+        <v>1.4081</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3671</v>
+        <v>1.4081</v>
       </c>
       <c r="N31" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3165</v>
+        <v>1.3557</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3267</v>
+        <v>0.3364</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1105</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3165</v>
+        <v>1.3557</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3165</v>
+        <v>1.3557</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3165</v>
+        <v>1.3557</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3165</v>
+        <v>1.3671</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3165</v>
+        <v>1.3671</v>
       </c>
       <c r="N32" t="n">
-        <v>87</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33">
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1863</v>
+        <v>1.1769</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2944</v>
+        <v>0.292</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0579</v>
+        <v>0.025</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1863</v>
+        <v>1.1769</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8465</v>
+        <v>0.8371</v>
       </c>
       <c r="G33" t="n">
         <v>0.3398</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8465</v>
+        <v>0.8371</v>
       </c>
       <c r="I33" t="n">
         <v>0.8584000000000001</v>
@@ -1974,7 +1974,7 @@
         <v>0.2361</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.037</v>
+        <v>-0.0648</v>
       </c>
       <c r="E34" t="n">
         <v>0.9515</v>
@@ -2010,139 +2010,139 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>z4KR</t>
+          <t>piriajr</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9132</v>
+        <v>0.9204</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2266</v>
+        <v>0.2284</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0524</v>
+        <v>-0.0772</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9132</v>
+        <v>0.9204</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9132</v>
+        <v>0.9204</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9132</v>
+        <v>0.9204</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9132</v>
+        <v>0.9281</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9132</v>
+        <v>0.9281</v>
       </c>
       <c r="N35" t="n">
-        <v>120</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kensizor</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8895</v>
+        <v>0.9132</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2207</v>
+        <v>0.2266</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.062</v>
+        <v>-0.0801</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8895</v>
+        <v>0.9132</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.0407</v>
+        <v>0.9132</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9302</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0407</v>
+        <v>0.9132</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0409</v>
+        <v>0.9132</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9302</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="L36" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8893</v>
+        <v>0.9132</v>
       </c>
       <c r="N36" t="n">
-        <v>207</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>piriajr</t>
+          <t>kensizor</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8849</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2196</v>
+        <v>0.2207</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0639</v>
+        <v>-0.0895</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8849</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8849</v>
+        <v>-0.0406</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.9302</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8849</v>
+        <v>-0.0406</v>
       </c>
       <c r="I37" t="n">
-        <v>0.889</v>
+        <v>-0.0409</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.9302</v>
       </c>
       <c r="K37" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M37" t="n">
-        <v>0.889</v>
+        <v>0.8893</v>
       </c>
       <c r="N37" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38">
@@ -2158,7 +2158,7 @@
         <v>0.2091</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0808</v>
+        <v>-0.1081</v>
       </c>
       <c r="E38" t="n">
         <v>0.8429</v>
@@ -2204,7 +2204,7 @@
         <v>0.2076</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0833</v>
+        <v>-0.1105</v>
       </c>
       <c r="E39" t="n">
         <v>0.8368</v>
@@ -2250,7 +2250,7 @@
         <v>0.1815</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1259</v>
+        <v>-0.1526</v>
       </c>
       <c r="E40" t="n">
         <v>0.7313</v>
@@ -2286,308 +2286,308 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6208</v>
+        <v>0.6996</v>
       </c>
       <c r="C41" t="n">
-        <v>0.154</v>
+        <v>0.1736</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1706</v>
+        <v>-0.1652</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6208</v>
+        <v>0.6996</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6208</v>
+        <v>0.6996</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6208</v>
+        <v>0.6996</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6208</v>
+        <v>0.6996</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6208</v>
+        <v>0.6996</v>
       </c>
       <c r="N41" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6116</v>
+        <v>0.6214</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1518</v>
+        <v>0.1542</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1743</v>
+        <v>-0.1963</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6116</v>
+        <v>0.6214</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6116</v>
+        <v>0.6214</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6116</v>
+        <v>0.6214</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6116</v>
+        <v>0.6214</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6116</v>
+        <v>0.6214</v>
       </c>
       <c r="N42" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5301</v>
+        <v>0.6116</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1315</v>
+        <v>0.1518</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2072</v>
+        <v>-0.2002</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5301</v>
+        <v>0.6116</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5301</v>
+        <v>0.6116</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5301</v>
+        <v>0.6116</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5326</v>
+        <v>0.6116</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5326</v>
+        <v>0.6116</v>
       </c>
       <c r="N43" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.439</v>
+        <v>0.5281</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1089</v>
+        <v>0.131</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.244</v>
+        <v>-0.2335</v>
       </c>
       <c r="E44" t="n">
-        <v>0.439</v>
+        <v>0.5281</v>
       </c>
       <c r="F44" t="n">
-        <v>0.439</v>
+        <v>0.5281</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.439</v>
+        <v>0.5281</v>
       </c>
       <c r="I44" t="n">
-        <v>0.439</v>
+        <v>0.5326</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.439</v>
+        <v>0.5326</v>
       </c>
       <c r="N44" t="n">
-        <v>62</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3164</v>
+        <v>0.439</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0785</v>
+        <v>0.1089</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2935</v>
+        <v>-0.269</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3164</v>
+        <v>0.439</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3164</v>
+        <v>0.439</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3164</v>
+        <v>0.439</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3164</v>
+        <v>0.439</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3164</v>
+        <v>0.439</v>
       </c>
       <c r="N45" t="n">
-        <v>158</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.293</v>
+        <v>0.3164</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0727</v>
+        <v>0.0785</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.303</v>
+        <v>-0.3179</v>
       </c>
       <c r="E46" t="n">
-        <v>0.293</v>
+        <v>0.3164</v>
       </c>
       <c r="F46" t="n">
-        <v>0.293</v>
+        <v>0.3164</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.293</v>
+        <v>0.3164</v>
       </c>
       <c r="I46" t="n">
-        <v>0.293</v>
+        <v>0.3164</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.293</v>
+        <v>0.3164</v>
       </c>
       <c r="N46" t="n">
-        <v>81</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2711</v>
+        <v>0.293</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0673</v>
+        <v>0.0727</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3118</v>
+        <v>-0.3272</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2711</v>
+        <v>0.293</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2711</v>
+        <v>0.293</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2711</v>
+        <v>0.293</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2711</v>
+        <v>0.293</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2711</v>
+        <v>0.293</v>
       </c>
       <c r="N47" t="n">
         <v>81</v>
@@ -2608,231 +2608,231 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2565</v>
+        <v>0.2711</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0636</v>
+        <v>0.0673</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3177</v>
+        <v>-0.3359</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2565</v>
+        <v>0.2711</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2565</v>
+        <v>0.2711</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2565</v>
+        <v>0.2711</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2565</v>
+        <v>0.2711</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2565</v>
+        <v>0.2711</v>
       </c>
       <c r="N48" t="n">
-        <v>141</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.248</v>
+        <v>0.2629</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0615</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3212</v>
+        <v>-0.3392</v>
       </c>
       <c r="E49" t="n">
-        <v>0.248</v>
+        <v>0.2629</v>
       </c>
       <c r="F49" t="n">
-        <v>0.248</v>
+        <v>0.2629</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.248</v>
+        <v>0.2629</v>
       </c>
       <c r="I49" t="n">
-        <v>0.248</v>
+        <v>0.2629</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.248</v>
+        <v>0.2629</v>
       </c>
       <c r="N49" t="n">
-        <v>87</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.2118</v>
+        <v>0.2497</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0526</v>
+        <v>0.062</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3358</v>
+        <v>-0.3444</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2118</v>
+        <v>0.2497</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2118</v>
+        <v>0.9161</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.6664</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2118</v>
+        <v>0.9161</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2118</v>
+        <v>0.9394</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.6664</v>
       </c>
       <c r="K50" t="n">
-        <v>62</v>
+        <v>193</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M50" t="n">
-        <v>0.2118</v>
+        <v>0.273</v>
       </c>
       <c r="N50" t="n">
-        <v>62</v>
+        <v>263</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1343</v>
+        <v>0.248</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0333</v>
+        <v>0.0615</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3671</v>
+        <v>-0.3451</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1343</v>
+        <v>0.248</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8007</v>
+        <v>0.248</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.6664</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8007</v>
+        <v>0.248</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.248</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.6664</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>193</v>
+        <v>87</v>
       </c>
       <c r="L51" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1456000000000001</v>
+        <v>0.248</v>
       </c>
       <c r="N51" t="n">
-        <v>263</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.2118</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0177</v>
+        <v>0.0526</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3925</v>
+        <v>-0.3595</v>
       </c>
       <c r="E52" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.2118</v>
       </c>
       <c r="F52" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.2118</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.2118</v>
       </c>
       <c r="I52" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.2118</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.2118</v>
       </c>
       <c r="N52" t="n">
-        <v>141</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53">
@@ -2848,7 +2848,7 @@
         <v>0.0176</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3927</v>
+        <v>-0.4156</v>
       </c>
       <c r="E53" t="n">
         <v>0.07099999999999999</v>
@@ -2884,645 +2884,645 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cairne</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0554</v>
+        <v>0.0674</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0137</v>
+        <v>0.0167</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.399</v>
+        <v>-0.4171</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0554</v>
+        <v>0.0674</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0554</v>
+        <v>0.0674</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0554</v>
+        <v>0.0674</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0554</v>
+        <v>0.0674</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0554</v>
+        <v>0.0674</v>
       </c>
       <c r="N54" t="n">
-        <v>81</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>cairne</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0486</v>
+        <v>0.0554</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0121</v>
+        <v>0.0137</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4017</v>
+        <v>-0.4218</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0486</v>
+        <v>0.0554</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0486</v>
+        <v>0.0554</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0486</v>
+        <v>0.0554</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0486</v>
+        <v>0.0554</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.0486</v>
+        <v>0.0554</v>
       </c>
       <c r="N55" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0077</v>
+        <v>0.0492</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0019</v>
+        <v>0.0122</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4245</v>
+        <v>-0.4243</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0077</v>
+        <v>0.0492</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0077</v>
+        <v>0.0492</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0077</v>
+        <v>0.0492</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0077</v>
+        <v>0.0492</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.0077</v>
+        <v>0.0492</v>
       </c>
       <c r="N56" t="n">
-        <v>141</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.0571</v>
+        <v>0.0008</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0142</v>
+        <v>0.0002</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4444</v>
+        <v>-0.4436</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0571</v>
+        <v>0.0008</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.0571</v>
+        <v>0.0008</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.0571</v>
+        <v>0.0008</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0571</v>
+        <v>0.0008</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.0571</v>
+        <v>0.0008</v>
       </c>
       <c r="N57" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.131</v>
+        <v>-0.0077</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0325</v>
+        <v>-0.0019</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4743</v>
+        <v>-0.447</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.131</v>
+        <v>-0.0077</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.131</v>
+        <v>-0.0077</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.131</v>
+        <v>-0.0077</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.131</v>
+        <v>-0.0077</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.131</v>
+        <v>-0.0077</v>
       </c>
       <c r="N58" t="n">
-        <v>92</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2188</v>
+        <v>-0.0571</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0543</v>
+        <v>-0.0142</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5098</v>
+        <v>-0.4667</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2188</v>
+        <v>-0.0571</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2188</v>
+        <v>-0.0571</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2188</v>
+        <v>-0.0571</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2188</v>
+        <v>-0.0571</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2188</v>
+        <v>-0.0571</v>
       </c>
       <c r="N59" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2457</v>
+        <v>-0.131</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.061</v>
+        <v>-0.0325</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5206</v>
+        <v>-0.4961</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2457</v>
+        <v>-0.131</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2457</v>
+        <v>-0.131</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.2457</v>
+        <v>-0.131</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2457</v>
+        <v>-0.131</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.2457</v>
+        <v>-0.131</v>
       </c>
       <c r="N60" t="n">
-        <v>120</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3651</v>
+        <v>-0.2457</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0906</v>
+        <v>-0.061</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5689</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3651</v>
+        <v>-0.2457</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.3651</v>
+        <v>-0.2457</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.3651</v>
+        <v>-0.2457</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3651</v>
+        <v>-0.2457</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3651</v>
+        <v>-0.2457</v>
       </c>
       <c r="N61" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4119</v>
+        <v>-0.3651</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1022</v>
+        <v>-0.0906</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5878</v>
+        <v>-0.5894</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4119</v>
+        <v>-0.3651</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.4119</v>
+        <v>-0.3651</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.4119</v>
+        <v>-0.3651</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.4119</v>
+        <v>-0.3651</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.4119</v>
+        <v>-0.3651</v>
       </c>
       <c r="N62" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4443</v>
+        <v>-0.4119</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1102</v>
+        <v>-0.1022</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6008</v>
+        <v>-0.608</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4443</v>
+        <v>-0.4119</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.4443</v>
+        <v>-0.4119</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.4443</v>
+        <v>-0.4119</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4443</v>
+        <v>-0.4119</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.4443</v>
+        <v>-0.4119</v>
       </c>
       <c r="N63" t="n">
-        <v>144</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4775</v>
+        <v>-0.4265</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1185</v>
+        <v>-0.1058</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6143</v>
+        <v>-0.6138</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4775</v>
+        <v>-0.4265</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4775</v>
+        <v>-0.4265</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.4775</v>
+        <v>-0.4265</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4775</v>
+        <v>-0.4265</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.4775</v>
+        <v>-0.4265</v>
       </c>
       <c r="N64" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.4777</v>
+        <v>-0.4775</v>
       </c>
       <c r="C65" t="n">
         <v>-0.1185</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6143</v>
+        <v>-0.6341</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.4777</v>
+        <v>-0.4775</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.4777</v>
+        <v>-0.4775</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.4777</v>
+        <v>-0.4775</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4777</v>
+        <v>-0.4775</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.4777</v>
+        <v>-0.4775</v>
       </c>
       <c r="N65" t="n">
-        <v>133</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>flashie</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4941</v>
+        <v>-0.4777</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1226</v>
+        <v>-0.1185</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.621</v>
+        <v>-0.6342</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4941</v>
+        <v>-0.4777</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4941</v>
+        <v>-0.4777</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4941</v>
+        <v>-0.4777</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4941</v>
+        <v>-0.4777</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4941</v>
+        <v>-0.4777</v>
       </c>
       <c r="N66" t="n">
-        <v>22</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>flashie</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5085</v>
+        <v>-0.4941</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1262</v>
+        <v>-0.1226</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.6268</v>
+        <v>-0.6408</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5085</v>
+        <v>-0.4941</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5085</v>
+        <v>-0.4941</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5085</v>
+        <v>-0.4941</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5085</v>
+        <v>-0.4941</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>133</v>
+        <v>22</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5085</v>
+        <v>-0.4941</v>
       </c>
       <c r="N67" t="n">
-        <v>133</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.6088</v>
+        <v>-0.6024</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.1511</v>
+        <v>-0.1495</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.6673</v>
+        <v>-0.6839</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.6088</v>
+        <v>-0.6024</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.6088</v>
+        <v>-0.6024</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.6088</v>
+        <v>-0.6024</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.6088</v>
+        <v>-0.6024</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.6088</v>
+        <v>-0.6024</v>
       </c>
       <c r="N68" t="n">
         <v>144</v>
@@ -3584,7 +3584,7 @@
         <v>-0.1532</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.6707</v>
+        <v>-0.6898</v>
       </c>
       <c r="E69" t="n">
         <v>-0.6173</v>
@@ -3630,7 +3630,7 @@
         <v>-0.1952</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7392</v>
+        <v>-0.7574</v>
       </c>
       <c r="E70" t="n">
         <v>-0.7868000000000001</v>
@@ -3676,7 +3676,7 @@
         <v>-0.226</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.7893</v>
+        <v>-0.8068</v>
       </c>
       <c r="E71" t="n">
         <v>-0.9109</v>
@@ -3722,7 +3722,7 @@
         <v>-0.2481</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E72" t="n">
         <v>-1</v>
@@ -3768,7 +3768,7 @@
         <v>-0.2837</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8832</v>
+        <v>-0.8994</v>
       </c>
       <c r="E73" t="n">
         <v>-1.1432</v>
@@ -3814,7 +3814,7 @@
         <v>-0.2837</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8833</v>
+        <v>-0.8994</v>
       </c>
       <c r="E74" t="n">
         <v>-1.1434</v>
@@ -3860,7 +3860,7 @@
         <v>-0.2986</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9075</v>
+        <v>-0.9233</v>
       </c>
       <c r="E75" t="n">
         <v>-1.2034</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.2901</v>
+        <v>-1.2856</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.3201</v>
+        <v>-0.319</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9425</v>
+        <v>-0.9560999999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.2901</v>
+        <v>-1.2856</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.3999</v>
+        <v>-0.3954</v>
       </c>
       <c r="G76" t="n">
         <v>-0.8902</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.3999</v>
+        <v>-0.3954</v>
       </c>
       <c r="I76" t="n">
         <v>-0.4055</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.4816</v>
+        <v>-1.4771</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.3676</v>
+        <v>-0.3665</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0199</v>
+        <v>-1.0324</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.4816</v>
+        <v>-1.4771</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.2005</v>
+        <v>-1.196</v>
       </c>
       <c r="G77" t="n">
         <v>-0.2811</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.2005</v>
+        <v>-1.196</v>
       </c>
       <c r="I77" t="n">
         <v>-1.2061</v>
@@ -3998,7 +3998,7 @@
         <v>-0.381</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0417</v>
+        <v>-1.0557</v>
       </c>
       <c r="E78" t="n">
         <v>-1.5356</v>
@@ -4044,7 +4044,7 @@
         <v>-0.4059</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0821</v>
+        <v>-1.0956</v>
       </c>
       <c r="E79" t="n">
         <v>-1.6357</v>
@@ -4090,7 +4090,7 @@
         <v>-0.4499</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1538</v>
+        <v>-1.1662</v>
       </c>
       <c r="E80" t="n">
         <v>-1.813</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.8554</v>
+        <v>-2.8462</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.7085</v>
+        <v>-0.7062</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5749</v>
+        <v>-1.5778</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.8554</v>
+        <v>-2.8462</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.4591</v>
+        <v>-2.4499</v>
       </c>
       <c r="G81" t="n">
         <v>-0.3963</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.4591</v>
+        <v>-2.4499</v>
       </c>
       <c r="I81" t="n">
         <v>-2.4705</v>
@@ -4182,7 +4182,7 @@
         <v>-1.0382</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.1116</v>
+        <v>-2.1108</v>
       </c>
       <c r="E82" t="n">
         <v>-4.1839</v>
@@ -4228,7 +4228,7 @@
         <v>-1.5369</v>
       </c>
       <c r="D83" t="n">
-        <v>-2.9235</v>
+        <v>-2.9115</v>
       </c>
       <c r="E83" t="n">
         <v>-6.1937</v>

--- a/database/event/8263/event_8263_evp_summary.xlsx
+++ b/database/event/8263/event_8263_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.0601</v>
+        <v>8.348699999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>2.0716</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0449</v>
+        <v>3.1154</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0601</v>
+        <v>8.348699999999999</v>
       </c>
       <c r="F2" t="n">
         <v>1.8693</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.1723</v>
+        <v>7.3654</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7797</v>
+        <v>1.8276</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6408</v>
+        <v>2.6761</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1723</v>
+        <v>7.3654</v>
       </c>
       <c r="F3" t="n">
         <v>2.9133</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4341</v>
+        <v>6.5606</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5965</v>
+        <v>1.6279</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3047</v>
+        <v>2.3167</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4341</v>
+        <v>6.5606</v>
       </c>
       <c r="F4" t="n">
         <v>1.9868</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.2415</v>
+        <v>6.4627</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5487</v>
+        <v>1.6036</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2171</v>
+        <v>2.2729</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2415</v>
+        <v>6.4627</v>
       </c>
       <c r="F5" t="n">
         <v>4.6779</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7958</v>
+        <v>6.1857</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4381</v>
+        <v>1.5349</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0142</v>
+        <v>2.1492</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7958</v>
+        <v>6.1857</v>
       </c>
       <c r="F6" t="n">
         <v>4.5807</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3705</v>
+        <v>4.7153</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0845</v>
+        <v>1.17</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3653</v>
+        <v>1.4924</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3705</v>
+        <v>4.7153</v>
       </c>
       <c r="F7" t="n">
         <v>4.0051</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3549</v>
+        <v>4.4612</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0806</v>
+        <v>1.107</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3582</v>
+        <v>1.3789</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3549</v>
+        <v>4.4612</v>
       </c>
       <c r="F8" t="n">
         <v>3.2928</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.2447</v>
+        <v>4.4041</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0532</v>
+        <v>1.0928</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3081</v>
+        <v>1.3534</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2447</v>
+        <v>4.4041</v>
       </c>
       <c r="F9" t="n">
         <v>2.9324</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1561</v>
+        <v>4.18</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0313</v>
+        <v>1.0372</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2677</v>
+        <v>1.2533</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1561</v>
+        <v>4.18</v>
       </c>
       <c r="F10" t="n">
         <v>2.3975</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.051</v>
+        <v>4.0941</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0052</v>
+        <v>1.0159</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2199</v>
+        <v>1.2149</v>
       </c>
       <c r="E11" t="n">
-        <v>4.051</v>
+        <v>4.0941</v>
       </c>
       <c r="F11" t="n">
         <v>1.7285</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5847</v>
+        <v>3.6373</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8895</v>
+        <v>0.9025</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0076</v>
+        <v>1.0109</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5847</v>
+        <v>3.6373</v>
       </c>
       <c r="F12" t="n">
         <v>3.3415</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kl1m</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5488</v>
+        <v>3.5989</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8806</v>
+        <v>0.893</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9913</v>
+        <v>0.9937</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5488</v>
+        <v>3.5989</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5215</v>
+        <v>3.0185</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0273</v>
+        <v>0.1135</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7246</v>
+        <v>3.8817</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6312</v>
+        <v>3.9817</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0273</v>
+        <v>0.1135</v>
       </c>
       <c r="K13" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L13" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6585</v>
+        <v>4.0952</v>
       </c>
       <c r="N13" t="n">
-        <v>186</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>kl1m</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.3953</v>
+        <v>3.4923</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8425</v>
+        <v>0.8665</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9214</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3953</v>
+        <v>3.4923</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5986</v>
+        <v>3.5215</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7967</v>
+        <v>0.0273</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5986</v>
+        <v>6.7246</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5986</v>
+        <v>3.6312</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7967</v>
+        <v>0.0273</v>
       </c>
       <c r="K14" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="L14" t="n">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3953</v>
+        <v>3.6585</v>
       </c>
       <c r="N14" t="n">
-        <v>328</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.3895</v>
+        <v>3.429</v>
       </c>
       <c r="C15" t="n">
-        <v>0.841</v>
+        <v>0.8508</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9188</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3895</v>
+        <v>3.429</v>
       </c>
       <c r="F15" t="n">
         <v>3.6027</v>
@@ -1136,277 +1136,277 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.2902</v>
+        <v>3.4177</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8164</v>
+        <v>0.848</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8736</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2902</v>
+        <v>3.4177</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6189</v>
+        <v>1.5986</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6713</v>
+        <v>1.7967</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0071</v>
+        <v>1.5986</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2456</v>
+        <v>1.5986</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6713</v>
+        <v>1.7967</v>
       </c>
       <c r="K16" t="n">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="L16" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9169</v>
+        <v>3.3953</v>
       </c>
       <c r="N16" t="n">
-        <v>263</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.2629</v>
+        <v>3.4128</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8096</v>
+        <v>0.8468</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8611</v>
+        <v>0.9106</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2629</v>
+        <v>3.4128</v>
       </c>
       <c r="F17" t="n">
-        <v>3.9196</v>
+        <v>2.6189</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6567</v>
+        <v>0.6713</v>
       </c>
       <c r="H17" t="n">
-        <v>8.0381</v>
+        <v>3.0071</v>
       </c>
       <c r="I17" t="n">
-        <v>4.3405</v>
+        <v>3.2456</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6567</v>
+        <v>0.6713</v>
       </c>
       <c r="K17" t="n">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="L17" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6838</v>
+        <v>3.9169</v>
       </c>
       <c r="N17" t="n">
-        <v>186</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.132</v>
+        <v>3.3171</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7771</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8015</v>
+        <v>0.8679</v>
       </c>
       <c r="E18" t="n">
-        <v>3.132</v>
+        <v>3.3171</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0185</v>
+        <v>3.0866</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1135</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8817</v>
+        <v>4.0307</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9817</v>
+        <v>4.0307</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1135</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>144</v>
       </c>
       <c r="L18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.0952</v>
+        <v>4.0307</v>
       </c>
       <c r="N18" t="n">
-        <v>207</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.0866</v>
+        <v>3.2489</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7659</v>
+        <v>0.8062</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7809</v>
+        <v>0.8374</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0866</v>
+        <v>3.2489</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0866</v>
+        <v>3.9196</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.6567</v>
       </c>
       <c r="H19" t="n">
-        <v>4.0307</v>
+        <v>8.0381</v>
       </c>
       <c r="I19" t="n">
-        <v>4.0307</v>
+        <v>4.3405</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.6567</v>
       </c>
       <c r="K19" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M19" t="n">
-        <v>4.0307</v>
+        <v>3.6838</v>
       </c>
       <c r="N19" t="n">
-        <v>144</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.9596</v>
+        <v>3.0117</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7473</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7231</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9596</v>
+        <v>3.0117</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1191</v>
+        <v>2.684</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1595</v>
+        <v>0.2614</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1019</v>
+        <v>3.9614</v>
       </c>
       <c r="I20" t="n">
-        <v>4.4272</v>
+        <v>2.1391</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1595</v>
+        <v>0.2614</v>
       </c>
       <c r="K20" t="n">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="L20" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2677</v>
+        <v>2.4005</v>
       </c>
       <c r="N20" t="n">
-        <v>331</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.9454</v>
+        <v>2.9633</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7308</v>
+        <v>0.7353</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7166</v>
+        <v>0.7098</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9454</v>
+        <v>2.9633</v>
       </c>
       <c r="F21" t="n">
-        <v>2.684</v>
+        <v>3.1191</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2614</v>
+        <v>-0.1595</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9614</v>
+        <v>4.1019</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1391</v>
+        <v>4.4272</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2614</v>
+        <v>-0.1595</v>
       </c>
       <c r="K21" t="n">
-        <v>124</v>
+        <v>205</v>
       </c>
       <c r="L21" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="M21" t="n">
-        <v>2.4005</v>
+        <v>4.2677</v>
       </c>
       <c r="N21" t="n">
-        <v>271</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22">
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6133</v>
+        <v>2.6661</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6484</v>
+        <v>0.6615</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5654</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6133</v>
+        <v>2.6661</v>
       </c>
       <c r="F22" t="n">
         <v>1.6968</v>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.4851</v>
+        <v>2.6168</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6166</v>
+        <v>0.6493</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5071</v>
+        <v>0.555</v>
       </c>
       <c r="E23" t="n">
-        <v>2.4851</v>
+        <v>2.6168</v>
       </c>
       <c r="F23" t="n">
         <v>2.4851</v>
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.4367</v>
+        <v>2.5148</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6046</v>
+        <v>0.624</v>
       </c>
       <c r="D24" t="n">
-        <v>0.485</v>
+        <v>0.5095</v>
       </c>
       <c r="E24" t="n">
-        <v>2.4367</v>
+        <v>2.5148</v>
       </c>
       <c r="F24" t="n">
         <v>2.4367</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.4262</v>
+        <v>2.4733</v>
       </c>
       <c r="C25" t="n">
-        <v>0.602</v>
+        <v>0.6137</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4803</v>
+        <v>0.4909</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4262</v>
+        <v>2.4733</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4262</v>
+        <v>2.3153</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.5852</v>
+        <v>2.3424</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6518</v>
+        <v>2.4028</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.6518</v>
+        <v>2.4028</v>
       </c>
       <c r="N25" t="n">
         <v>154</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.3153</v>
+        <v>2.4196</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5745</v>
+        <v>0.6004</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4298</v>
+        <v>0.467</v>
       </c>
       <c r="E26" t="n">
-        <v>2.3153</v>
+        <v>2.4196</v>
       </c>
       <c r="F26" t="n">
-        <v>2.3153</v>
+        <v>2.4262</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.3424</v>
+        <v>2.5852</v>
       </c>
       <c r="I26" t="n">
-        <v>2.4028</v>
+        <v>2.6518</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.4028</v>
+        <v>2.6518</v>
       </c>
       <c r="N26" t="n">
         <v>154</v>
@@ -1646,16 +1646,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.1519</v>
+        <v>2.2272</v>
       </c>
       <c r="C27" t="n">
-        <v>0.534</v>
+        <v>0.5526</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3554</v>
+        <v>0.381</v>
       </c>
       <c r="E27" t="n">
-        <v>2.1519</v>
+        <v>2.2272</v>
       </c>
       <c r="F27" t="n">
         <v>2.1519</v>
@@ -1688,277 +1688,277 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.1303</v>
+        <v>2.0272</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5286</v>
+        <v>0.503</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3456</v>
+        <v>0.2917</v>
       </c>
       <c r="E28" t="n">
-        <v>2.1303</v>
+        <v>2.0272</v>
       </c>
       <c r="F28" t="n">
-        <v>2.1303</v>
+        <v>1.6359</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.1303</v>
+        <v>1.6359</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1303</v>
+        <v>1.6359</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.1303</v>
+        <v>1.6359</v>
       </c>
       <c r="N28" t="n">
-        <v>120</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>alex666</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9417</v>
+        <v>2.0145</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4818</v>
+        <v>0.4999</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2597</v>
+        <v>0.286</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9417</v>
+        <v>2.0145</v>
       </c>
       <c r="F29" t="n">
-        <v>2.2554</v>
+        <v>2.1303</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3137</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.2554</v>
+        <v>2.1303</v>
       </c>
       <c r="I29" t="n">
-        <v>2.3135</v>
+        <v>2.1303</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3137</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="L29" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.9998</v>
+        <v>2.1303</v>
       </c>
       <c r="N29" t="n">
-        <v>207</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>alex666</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.7201</v>
+        <v>1.8877</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4268</v>
+        <v>0.4684</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1588</v>
+        <v>0.2294</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7201</v>
+        <v>1.8877</v>
       </c>
       <c r="F30" t="n">
-        <v>1.7201</v>
+        <v>2.2554</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.3137</v>
       </c>
       <c r="H30" t="n">
-        <v>1.7201</v>
+        <v>2.2554</v>
       </c>
       <c r="I30" t="n">
-        <v>1.7644</v>
+        <v>2.3135</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.3137</v>
       </c>
       <c r="K30" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M30" t="n">
-        <v>1.7644</v>
+        <v>1.9998</v>
       </c>
       <c r="N30" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.6359</v>
+        <v>1.8419</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4059</v>
+        <v>0.457</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1205</v>
+        <v>0.2089</v>
       </c>
       <c r="E31" t="n">
-        <v>1.6359</v>
+        <v>1.8419</v>
       </c>
       <c r="F31" t="n">
-        <v>1.6359</v>
+        <v>1.7201</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.6359</v>
+        <v>1.7201</v>
       </c>
       <c r="I31" t="n">
-        <v>1.6359</v>
+        <v>1.7644</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.6359</v>
+        <v>1.7644</v>
       </c>
       <c r="N31" t="n">
-        <v>87</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>cobrazera</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.5858</v>
+        <v>1.6261</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3935</v>
+        <v>0.4035</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0977</v>
+        <v>0.1125</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5858</v>
+        <v>1.6261</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5858</v>
+        <v>1.2391</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.3377</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5858</v>
+        <v>1.2391</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5858</v>
+        <v>1.3374</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.3377</v>
       </c>
       <c r="K32" t="n">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M32" t="n">
-        <v>1.5858</v>
+        <v>1.6751</v>
       </c>
       <c r="N32" t="n">
-        <v>136</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cobrazera</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.5768</v>
+        <v>1.6067</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3913</v>
+        <v>0.3987</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0936</v>
+        <v>0.1039</v>
       </c>
       <c r="E33" t="n">
-        <v>1.5768</v>
+        <v>1.6067</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2391</v>
+        <v>1.5858</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3377</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2391</v>
+        <v>1.5858</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3374</v>
+        <v>1.5858</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3377</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="L33" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.6751</v>
+        <v>1.5858</v>
       </c>
       <c r="N33" t="n">
-        <v>263</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34">
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.3889</v>
+        <v>1.3689</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3446</v>
+        <v>0.3397</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0081</v>
+        <v>-0.0024</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3889</v>
+        <v>1.3689</v>
       </c>
       <c r="F34" t="n">
         <v>0.3768</v>
@@ -2010,124 +2010,124 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>piriajr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.2383</v>
+        <v>1.3037</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3073</v>
+        <v>0.3235</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0605</v>
+        <v>-0.0315</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2383</v>
+        <v>1.3037</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2383</v>
+        <v>1.0866</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2383</v>
+        <v>1.0866</v>
       </c>
       <c r="I35" t="n">
-        <v>1.2702</v>
+        <v>1.0866</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.2702</v>
+        <v>1.0866</v>
       </c>
       <c r="N35" t="n">
-        <v>154</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>piriajr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.1813</v>
+        <v>1.2782</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2931</v>
+        <v>0.3172</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0429</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1813</v>
+        <v>1.2782</v>
       </c>
       <c r="F36" t="n">
-        <v>1.1813</v>
+        <v>1.2383</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.1813</v>
+        <v>1.2383</v>
       </c>
       <c r="I36" t="n">
-        <v>1.1813</v>
+        <v>1.2702</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1813</v>
+        <v>1.2702</v>
       </c>
       <c r="N36" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.1579</v>
+        <v>1.25</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2873</v>
+        <v>0.3102</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0555</v>
       </c>
       <c r="E37" t="n">
-        <v>1.1579</v>
+        <v>1.25</v>
       </c>
       <c r="F37" t="n">
-        <v>1.1579</v>
+        <v>1.1813</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.1579</v>
+        <v>1.1813</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1579</v>
+        <v>1.1813</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1579</v>
+        <v>1.1813</v>
       </c>
       <c r="N37" t="n">
         <v>158</v>
@@ -2148,400 +2148,400 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.1344</v>
+        <v>1.1909</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2815</v>
+        <v>0.2955</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1078</v>
+        <v>-0.0819</v>
       </c>
       <c r="E38" t="n">
-        <v>1.1344</v>
+        <v>1.1909</v>
       </c>
       <c r="F38" t="n">
-        <v>1.1344</v>
+        <v>0.9715</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.1344</v>
+        <v>0.9715</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1636</v>
+        <v>0.9715</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>154</v>
+        <v>92</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1636</v>
+        <v>0.9715</v>
       </c>
       <c r="N38" t="n">
-        <v>154</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.1336</v>
+        <v>1.1849</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2813</v>
+        <v>0.294</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1082</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>1.1336</v>
+        <v>1.1849</v>
       </c>
       <c r="F39" t="n">
-        <v>1.1336</v>
+        <v>1.1579</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.1336</v>
+        <v>1.1579</v>
       </c>
       <c r="I39" t="n">
-        <v>1.1336</v>
+        <v>1.1579</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.1336</v>
+        <v>1.1579</v>
       </c>
       <c r="N39" t="n">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>z4KR</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.0866</v>
+        <v>1.1562</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2696</v>
+        <v>0.2869</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1296</v>
+        <v>-0.0974</v>
       </c>
       <c r="E40" t="n">
-        <v>1.0866</v>
+        <v>1.1562</v>
       </c>
       <c r="F40" t="n">
-        <v>1.0866</v>
+        <v>1.1344</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.0866</v>
+        <v>1.1344</v>
       </c>
       <c r="I40" t="n">
-        <v>1.0866</v>
+        <v>1.1636</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.0866</v>
+        <v>1.1636</v>
       </c>
       <c r="N40" t="n">
-        <v>120</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.0005</v>
+        <v>1.1403</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2483</v>
+        <v>0.2829</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1688</v>
+        <v>-0.1045</v>
       </c>
       <c r="E41" t="n">
-        <v>1.0005</v>
+        <v>1.1403</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0005</v>
+        <v>1.1336</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.0005</v>
+        <v>1.1336</v>
       </c>
       <c r="I41" t="n">
-        <v>1.0005</v>
+        <v>1.1336</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.0005</v>
+        <v>1.1336</v>
       </c>
       <c r="N41" t="n">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9715</v>
+        <v>1.091</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2411</v>
+        <v>0.2707</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.182</v>
+        <v>-0.1265</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9715</v>
+        <v>1.091</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9715</v>
+        <v>1.0005</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9715</v>
+        <v>1.0005</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9715</v>
+        <v>1.0005</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9715</v>
+        <v>1.0005</v>
       </c>
       <c r="N42" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9207</v>
+        <v>0.9127</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2285</v>
+        <v>0.2265</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2051</v>
+        <v>-0.2061</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9207</v>
+        <v>0.9127</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9207</v>
+        <v>0.608</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9207</v>
+        <v>0.608</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9207</v>
+        <v>0.608</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9207</v>
+        <v>0.608</v>
       </c>
       <c r="N43" t="n">
-        <v>141</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6993</v>
+        <v>0.904</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1735</v>
+        <v>0.2243</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3059</v>
+        <v>-0.21</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6993</v>
+        <v>0.904</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6993</v>
+        <v>0.5726</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6993</v>
+        <v>0.5726</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6993</v>
+        <v>0.5726</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6993</v>
+        <v>0.5726</v>
       </c>
       <c r="N44" t="n">
-        <v>133</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6931</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>0.172</v>
+        <v>0.1917</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3087</v>
+        <v>-0.2687</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6931</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6931</v>
+        <v>0.6015</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6931</v>
+        <v>0.6015</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6931</v>
+        <v>0.6015</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6931</v>
+        <v>0.6015</v>
       </c>
       <c r="N45" t="n">
-        <v>141</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6105</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1515</v>
+        <v>0.1912</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3463</v>
+        <v>-0.2696</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6105</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6105</v>
+        <v>0.4626</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6105</v>
+        <v>0.4626</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6105</v>
+        <v>0.4626</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6105</v>
+        <v>0.4626</v>
       </c>
       <c r="N46" t="n">
         <v>81</v>
@@ -2562,185 +2562,185 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.608</v>
+        <v>0.7541</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1509</v>
+        <v>0.1871</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3474</v>
+        <v>-0.277</v>
       </c>
       <c r="E47" t="n">
-        <v>0.608</v>
+        <v>0.7541</v>
       </c>
       <c r="F47" t="n">
-        <v>0.608</v>
+        <v>0.6105</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.608</v>
+        <v>0.6105</v>
       </c>
       <c r="I47" t="n">
-        <v>0.608</v>
+        <v>0.6105</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.608</v>
+        <v>0.6105</v>
       </c>
       <c r="N47" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6015</v>
+        <v>0.7398</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1493</v>
+        <v>0.1836</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3504</v>
+        <v>-0.2834</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6015</v>
+        <v>0.7398</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6015</v>
+        <v>0.9207</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6015</v>
+        <v>0.9207</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6015</v>
+        <v>0.9207</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6015</v>
+        <v>0.9207</v>
       </c>
       <c r="N48" t="n">
-        <v>92</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5846</v>
+        <v>0.7101</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1451</v>
+        <v>0.1762</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3581</v>
+        <v>-0.2966</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5846</v>
+        <v>0.7101</v>
       </c>
       <c r="F49" t="n">
-        <v>1.0345</v>
+        <v>0.6993</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.4499</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.0345</v>
+        <v>0.6993</v>
       </c>
       <c r="I49" t="n">
-        <v>1.1166</v>
+        <v>0.6993</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.4499</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="L49" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.6993</v>
       </c>
       <c r="N49" t="n">
-        <v>263</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5726</v>
+        <v>0.7013</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1421</v>
+        <v>0.174</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3635</v>
+        <v>-0.3006</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5726</v>
+        <v>0.7013</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5726</v>
+        <v>0.6931</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5726</v>
+        <v>0.6931</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5726</v>
+        <v>0.6931</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.5726</v>
+        <v>0.6931</v>
       </c>
       <c r="N50" t="n">
-        <v>62</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51">
@@ -2750,16 +2750,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.5769</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1254</v>
+        <v>0.1431</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3941</v>
+        <v>-0.3561</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.5769</v>
       </c>
       <c r="F51" t="n">
         <v>0.5054999999999999</v>
@@ -2792,231 +2792,231 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.479</v>
+        <v>0.4921</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1189</v>
+        <v>0.1221</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4062</v>
+        <v>-0.394</v>
       </c>
       <c r="E52" t="n">
-        <v>0.479</v>
+        <v>0.4921</v>
       </c>
       <c r="F52" t="n">
-        <v>0.479</v>
+        <v>0.3171</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.479</v>
+        <v>0.3171</v>
       </c>
       <c r="I52" t="n">
-        <v>0.479</v>
+        <v>0.3171</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.479</v>
+        <v>0.3171</v>
       </c>
       <c r="N52" t="n">
-        <v>158</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4626</v>
+        <v>0.436</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1148</v>
+        <v>0.1082</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4136</v>
+        <v>-0.4191</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4626</v>
+        <v>0.436</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4626</v>
+        <v>1.0345</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.4499</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4626</v>
+        <v>1.0345</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4626</v>
+        <v>1.1166</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.4499</v>
       </c>
       <c r="K53" t="n">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4626</v>
+        <v>0.6667000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>81</v>
+        <v>263</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cairne</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4588</v>
+        <v>0.3422</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1138</v>
+        <v>0.0849</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4153</v>
+        <v>-0.461</v>
       </c>
       <c r="E54" t="n">
-        <v>0.4588</v>
+        <v>0.3422</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4588</v>
+        <v>0.4318</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.4588</v>
+        <v>0.4318</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4588</v>
+        <v>0.4318</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4588</v>
+        <v>0.4318</v>
       </c>
       <c r="N54" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4318</v>
+        <v>0.3403</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1071</v>
+        <v>0.0844</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4276</v>
+        <v>-0.4618</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4318</v>
+        <v>0.3403</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4318</v>
+        <v>0.479</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4318</v>
+        <v>0.479</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4318</v>
+        <v>0.479</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4318</v>
+        <v>0.479</v>
       </c>
       <c r="N55" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.3171</v>
+        <v>0.3278</v>
       </c>
       <c r="C56" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0813</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4799</v>
+        <v>-0.4674</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3171</v>
+        <v>0.3278</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3171</v>
+        <v>0.057</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3171</v>
+        <v>0.057</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3171</v>
+        <v>0.057</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.3171</v>
+        <v>0.057</v>
       </c>
       <c r="N56" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57">
@@ -3026,16 +3026,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2499</v>
+        <v>0.2001</v>
       </c>
       <c r="C57" t="n">
-        <v>0.062</v>
+        <v>0.0497</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5104</v>
+        <v>-0.5244</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2499</v>
+        <v>0.2001</v>
       </c>
       <c r="F57" t="n">
         <v>0.2499</v>
@@ -3068,93 +3068,93 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>cairne</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.1778</v>
+        <v>0.1738</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0441</v>
+        <v>0.0431</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5433</v>
+        <v>-0.5362</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1778</v>
+        <v>0.1738</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1778</v>
+        <v>0.4588</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1778</v>
+        <v>0.4588</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1778</v>
+        <v>0.4588</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1778</v>
+        <v>0.4588</v>
       </c>
       <c r="N58" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.1523</v>
+        <v>0.019</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0378</v>
+        <v>0.0047</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1523</v>
+        <v>0.019</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1523</v>
+        <v>0.1778</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1523</v>
+        <v>0.1778</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1523</v>
+        <v>0.1778</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1523</v>
+        <v>0.1778</v>
       </c>
       <c r="N59" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60">
@@ -3164,16 +3164,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.1136</v>
+        <v>-0.1019</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0282</v>
+        <v>-0.0253</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5725</v>
+        <v>-0.6593</v>
       </c>
       <c r="E60" t="n">
-        <v>0.1136</v>
+        <v>-0.1019</v>
       </c>
       <c r="F60" t="n">
         <v>0.1136</v>
@@ -3206,277 +3206,277 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.057</v>
+        <v>-0.1989</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0141</v>
+        <v>-0.0494</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.7027</v>
       </c>
       <c r="E61" t="n">
-        <v>0.057</v>
+        <v>-0.1989</v>
       </c>
       <c r="F61" t="n">
-        <v>0.057</v>
+        <v>-0.0121</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.057</v>
+        <v>-0.0121</v>
       </c>
       <c r="I61" t="n">
-        <v>0.057</v>
+        <v>-0.0121</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.057</v>
+        <v>-0.0121</v>
       </c>
       <c r="N61" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>xKacpersky</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.0121</v>
+        <v>-0.2366</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.003</v>
+        <v>-0.0587</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6297</v>
+        <v>-0.7195</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0121</v>
+        <v>-0.2366</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.0121</v>
+        <v>-0.2826</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.0121</v>
+        <v>-0.2826</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0121</v>
+        <v>-0.2826</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.0121</v>
+        <v>-0.2826</v>
       </c>
       <c r="N62" t="n">
-        <v>133</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.0765</v>
+        <v>-0.2432</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.019</v>
+        <v>-0.0603</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.659</v>
+        <v>-0.7225</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.0765</v>
+        <v>-0.2432</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6489</v>
+        <v>-0.1458</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.7254</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6489</v>
+        <v>-0.1458</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3504</v>
+        <v>-0.1458</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.7254</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="L63" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3750000000000001</v>
+        <v>-0.1458</v>
       </c>
       <c r="N63" t="n">
-        <v>186</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.1415</v>
+        <v>-0.2545</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.0351</v>
+        <v>-0.0631</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6886</v>
+        <v>-0.7275</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.1415</v>
+        <v>-0.2545</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.1415</v>
+        <v>0.6489</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>-0.7254</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.1415</v>
+        <v>0.6489</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1415</v>
+        <v>0.3504</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>-0.7254</v>
       </c>
       <c r="K64" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.1415</v>
+        <v>-0.3750000000000001</v>
       </c>
       <c r="N64" t="n">
-        <v>144</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.1458</v>
+        <v>-0.2617</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0362</v>
+        <v>-0.0649</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6906</v>
+        <v>-0.7307</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.1458</v>
+        <v>-0.2617</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.1458</v>
+        <v>0.1523</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.1458</v>
+        <v>0.1523</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1458</v>
+        <v>0.1523</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.1458</v>
+        <v>0.1523</v>
       </c>
       <c r="N65" t="n">
-        <v>133</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.1584</v>
+        <v>-0.29</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.0393</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6963</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.1584</v>
+        <v>-0.29</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.1584</v>
+        <v>-0.1415</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.1584</v>
+        <v>-0.1415</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1584</v>
+        <v>-0.1415</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.1584</v>
+        <v>-0.1415</v>
       </c>
       <c r="N66" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67">
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.2016</v>
+        <v>-0.3523</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.05</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.716</v>
+        <v>-0.7712</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.2016</v>
+        <v>-0.3523</v>
       </c>
       <c r="F67" t="n">
         <v>0.3789</v>
@@ -3528,323 +3528,323 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.2683</v>
+        <v>-0.4098</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.1017</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7463</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.2683</v>
+        <v>-0.4098</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.2683</v>
+        <v>-0.1584</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.2683</v>
+        <v>-0.1584</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2683</v>
+        <v>-0.1584</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.2683</v>
+        <v>-0.1584</v>
       </c>
       <c r="N68" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>xKacpersky</t>
+          <t>flashie</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.2826</v>
+        <v>-0.4707</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.0701</v>
+        <v>-0.1168</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7528</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.2826</v>
+        <v>-0.4707</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.2826</v>
+        <v>-0.3325</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.2826</v>
+        <v>-0.3325</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2826</v>
+        <v>-0.3325</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.2826</v>
+        <v>-0.3325</v>
       </c>
       <c r="N69" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>flashie</t>
+          <t>xiELO</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.3325</v>
+        <v>-0.55</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.0825</v>
+        <v>-0.1365</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7756</v>
+        <v>-0.8595</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.3325</v>
+        <v>-0.55</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.3325</v>
+        <v>-0.4006</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.3325</v>
+        <v>-0.4006</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3325</v>
+        <v>-0.4006</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.3325</v>
+        <v>-0.4006</v>
       </c>
       <c r="N70" t="n">
-        <v>22</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>xiELO</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.4006</v>
+        <v>-0.5948</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.0994</v>
+        <v>-0.1476</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8066</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.4006</v>
+        <v>-0.5948</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.4006</v>
+        <v>-0.5004</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.4006</v>
+        <v>-0.5004</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4006</v>
+        <v>-0.5004</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>144</v>
+        <v>87</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.4006</v>
+        <v>-0.5004</v>
       </c>
       <c r="N71" t="n">
-        <v>144</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.5004</v>
+        <v>-0.642</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.1242</v>
+        <v>-0.1593</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.852</v>
+        <v>-0.9006</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.5004</v>
+        <v>-0.642</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.5004</v>
+        <v>-0.2683</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.5004</v>
+        <v>-0.2683</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.5004</v>
+        <v>-0.2683</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.5004</v>
+        <v>-0.2683</v>
       </c>
       <c r="N72" t="n">
-        <v>87</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ScrunK</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.6301</v>
+        <v>-0.7527</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.1563</v>
+        <v>-0.1868</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.911</v>
+        <v>-0.95</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.6301</v>
+        <v>-0.7527</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6301</v>
+        <v>-0.6409</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6301</v>
+        <v>-0.6409</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.6301</v>
+        <v>-0.6409</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.6301</v>
+        <v>-0.6409</v>
       </c>
       <c r="N73" t="n">
-        <v>62</v>
+        <v>133</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>s1zzi</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.6409</v>
+        <v>-0.9698</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.159</v>
+        <v>-0.2406</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.916</v>
+        <v>-1.047</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.6409</v>
+        <v>-0.9698</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.6409</v>
+        <v>-0.7295</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>-0.2037</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.6409</v>
+        <v>-0.7295</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.6409</v>
+        <v>-0.7483</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>-0.2037</v>
       </c>
       <c r="K74" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.6409</v>
+        <v>-0.952</v>
       </c>
       <c r="N74" t="n">
-        <v>133</v>
+        <v>207</v>
       </c>
     </row>
     <row r="75">
@@ -3854,16 +3854,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.6866</v>
+        <v>-1.054</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.1704</v>
+        <v>-0.2615</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9368</v>
+        <v>-1.0846</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.6866</v>
+        <v>-1.054</v>
       </c>
       <c r="F75" t="n">
         <v>-0.6866</v>
@@ -3896,139 +3896,139 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>s1zzi</t>
+          <t>ScrunK</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.9332</v>
+        <v>-1.0931</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.2316</v>
+        <v>-0.2712</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.049</v>
+        <v>-1.1021</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.9332</v>
+        <v>-1.0931</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.7295</v>
+        <v>-0.6301</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.2037</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.7295</v>
+        <v>-0.6301</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7483</v>
+        <v>-0.6301</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.2037</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="L76" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.952</v>
+        <v>-0.6301</v>
       </c>
       <c r="N76" t="n">
-        <v>207</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>krazy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1</v>
+        <v>-1.3144</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.2481</v>
+        <v>-0.3261</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0794</v>
+        <v>-1.2009</v>
       </c>
       <c r="E77" t="n">
-        <v>-1</v>
+        <v>-1.3144</v>
       </c>
       <c r="F77" t="n">
-        <v>-1</v>
+        <v>-1.0763</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1</v>
+        <v>-1.0763</v>
       </c>
       <c r="I77" t="n">
-        <v>-1</v>
+        <v>-1.0763</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1</v>
+        <v>-1.0763</v>
       </c>
       <c r="N77" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>krazy</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.0763</v>
+        <v>-1.443</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.2671</v>
+        <v>-0.3581</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1142</v>
+        <v>-1.2584</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.0763</v>
+        <v>-1.443</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.0763</v>
+        <v>-1</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.0763</v>
+        <v>-1</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.0763</v>
+        <v>-1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.0763</v>
+        <v>-1</v>
       </c>
       <c r="N78" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.2888</v>
+        <v>-1.4712</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.3198</v>
+        <v>-0.3651</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2109</v>
+        <v>-1.271</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.2888</v>
+        <v>-1.4712</v>
       </c>
       <c r="F79" t="n">
         <v>-1.2888</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.307</v>
+        <v>-1.5572</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.3243</v>
+        <v>-0.3864</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2192</v>
+        <v>-1.3094</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.307</v>
+        <v>-1.5572</v>
       </c>
       <c r="F80" t="n">
         <v>-1.307</v>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.0386</v>
+        <v>-2.2637</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.5058</v>
+        <v>-0.5617</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5522</v>
+        <v>-1.625</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.0386</v>
+        <v>-2.2637</v>
       </c>
       <c r="F81" t="n">
         <v>-1.8444</v>
@@ -4176,16 +4176,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3.3948</v>
+        <v>-3.55</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.8424</v>
+        <v>-0.8809</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.1696</v>
+        <v>-2.1995</v>
       </c>
       <c r="E82" t="n">
-        <v>-3.3948</v>
+        <v>-3.55</v>
       </c>
       <c r="F82" t="n">
         <v>-1.0378</v>
@@ -4222,16 +4222,16 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-7.3799</v>
+        <v>-7.703</v>
       </c>
       <c r="C83" t="n">
-        <v>-1.8312</v>
+        <v>-1.9114</v>
       </c>
       <c r="D83" t="n">
-        <v>-3.9837</v>
+        <v>-4.0546</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.3799</v>
+        <v>-7.703</v>
       </c>
       <c r="F83" t="n">
         <v>-5.3799</v>
